--- a/internal_doc/05.测试设计/story/数据压缩/compress测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/数据压缩/compress测试设计.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="1" r:id="rId1"/>
-    <sheet name="compress测试点" sheetId="2" r:id="rId2"/>
+    <sheet name="功能测试" sheetId="2" r:id="rId2"/>
     <sheet name="可靠性测试" sheetId="4" r:id="rId3"/>
+    <sheet name="其他场景测试" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -21,7 +22,71 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A29" authorId="0">
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+跟</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LZW</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>压缩中修改</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>测试点重复</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +335,99 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-从小记录变成大记录，更新后记录正确性</t>
+从小记录变成大记录，更新后记录正确性，覆盖：
+1、update更新已存在的记录使原记录变大；
+2、upsert更新不存在的记录使记录数增加同时增加记录大小；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+在第</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>个测试点已覆盖</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C53" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+在第</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>个测试点已覆盖</t>
         </r>
       </text>
     </comment>
@@ -301,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A70" authorId="0">
+    <comment ref="C72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -349,77 +506,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-待确认是否支持</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A76" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-增删改查时删除</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>CL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>，查看返回结果；循环多次操作</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C88" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>huangxiaoni:</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>放到性能里面测试</t>
+待确认是否支持
+--SQL不能指定压缩类型，SQL无需测试</t>
         </r>
       </text>
     </comment>
@@ -433,7 +521,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="B2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -460,7 +548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -483,6 +571,164 @@
           </rPr>
           <t xml:space="preserve">
 重点关注目标组异常，源组可以不用关注</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+交叉覆盖</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+切分过程没有变动，只需简单覆盖</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+交叉覆盖</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+增删改查时删除</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，查看返回结果；循环多次操作</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>huangxiaoni:</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>放到性能里面测试</t>
         </r>
       </text>
     </comment>
@@ -491,7 +737,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="189">
   <si>
     <t>压缩方式</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -522,10 +768,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>特性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>测试点</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -590,35 +832,14 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>集群模式</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>单机</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>3组3节点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>支持单机、集群模式</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询（find、query、aggregate）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>事务</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>开启压缩后，不支持修改关闭压缩；
-指定压缩算法后不支持修改压缩算法。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>插入记录数&gt;100条，总记录大小&lt;10M</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -667,35 +888,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>数据压缩后执行事务操作，包括事务提交和回滚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SQL</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>正常场景-数据压缩功能测试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>bulkInsert批量插入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入记录，记录中子串重复率高</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入记录，记录中子串重复率低</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CL删除成功，元数据及数据文件均被删除，包括字典</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>构建字典并压缩记录后删除CL</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -804,18 +1001,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>修改失败</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可靠性测试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>全网掉电</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -845,10 +1030,6 @@
   </si>
   <si>
     <t>备节点异常重启</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据已压缩，并发做增删改查操作时数据节点异常</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -979,10 +1160,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>aggregate查询</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>存在索引，增删改查数据</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1008,20 +1185,11 @@
   </si>
   <si>
     <t>原有功能可用，新增lzw压缩不影响原有功能正确性</t>
-  </si>
-  <si>
-    <t>新增压缩算法，需要验证集合/数据操作lzw压缩功能</t>
-  </si>
-  <si>
-    <t>创建lzw压缩表，覆盖不同集合类型</t>
   </si>
   <si>
     <t>1、切分成功，源组和目标组数据正确；snapshot查看目标组集合跟源组集合压缩属性一致，均为lzw压缩
 2、再次插入源组范围内的记录，记录有压缩且正确
 3、再次插入目标组范围内的记录，记录有压缩且正确</t>
-  </si>
-  <si>
-    <t>执行SQL创建CL，并指定lzw压缩</t>
   </si>
   <si>
     <t>lzw压缩</t>
@@ -1093,13 +1261,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、新增压缩算法对原有压缩方式（不开启压缩、开启Snappy压缩）不影响
-2、新增压缩算法需要保证数据库操作、数据操作功能正确性，且压缩比要有明显提升
-3、性能需要比原来的有所提升
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>创建CL</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1117,10 +1278,6 @@
   </si>
   <si>
     <t>lzw压缩(Compressed:ture,CompressionType:"lzw")</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建普通表，指定压缩算法为lzw压缩</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1164,6 +1321,105 @@
 1、常用更新符
 2、单条记录更新
 3、指定范围批量更新</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录压缩后查询记录,覆盖：
+1、常用匹配符
+2、覆盖所有的查询符（包括hint、limit、skip……）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggregate查询记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、切分成功，源组和目标组数据正确；snapshot查看目标组集合跟源组集合压缩属性一致，均为lzw压缩
+2、再次插入源组范围内的记录，记录有压缩且正确
+3、再次插入目标组范围内的记录，插入记录达到压缩条件后数据有压缩，且压缩后数据正确</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>源组切到目标组，目标组数据没有达到构建字典条件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>源组切到目标组，目标组数据达到构建字典条件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据压缩后，执行SQL增删改查记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引的同时插入数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引的同时查询数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼容老版本，老版本升级到新版本如下功能正常可用：
+1、升级前后，不开启压缩，数据操作等基本功能正常可用
+2、升级前后，开启Snappy压缩，数据操作等基本功能正常可用
+3、升级后，开启lzw压缩，数据操作等基本功能正常可用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点所在主机内存满</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、删除CL删除成功
+2、新创建的同名CL正常可用，插入数据，数据可正常压缩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不开启压缩，在表中插入大量数据（如1G），修改为snappy压缩后再次插入大量记录（如1G）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>批量更新已压缩和未压缩的记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志满导致事务回滚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试字典是否有无限膨胀的情况</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点所在主机磁盘满</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点所在主机CPU满</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定压缩算法为lzw压缩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>插入记录</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，记录间有重复子串</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1172,6 +1428,7 @@
     </r>
     <r>
       <rPr>
+        <i/>
         <strike/>
         <sz val="11"/>
         <color theme="1"/>
@@ -1195,99 +1452,106 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>记录压缩后查询记录,覆盖：
-1、常用匹配符
-2、覆盖所有的查询符（包括hint、limit、skip……）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>aggregate查询记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、切分成功，源组和目标组数据正确；snapshot查看目标组集合跟源组集合压缩属性一致，均为lzw压缩
-2、再次插入源组范围内的记录，记录有压缩且正确
-3、再次插入目标组范围内的记录，插入记录达到压缩条件后数据有压缩，且压缩后数据正确</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>源组切到目标组，目标组数据没有达到构建字典条件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>源组切到目标组，目标组数据达到构建字典条件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据压缩后，执行SQL增删改查记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引的同时插入数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引的同时查询数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>兼容老版本，老版本升级到新版本如下功能正常可用：
-1、升级前后，不开启压缩，数据操作等基本功能正常可用
-2、升级前后，开启Snappy压缩，数据操作等基本功能正常可用
-3、升级后，开启lzw压缩，数据操作等基本功能正常可用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>lzw表，数据未压缩，节点异常后批量插入数据（构建字典过程中）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点所在主机内存满</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入记录，记录间有重复子串</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入记录，记录中无重复的子串</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CL数据已压缩，删除CL后创建同名CL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、删除CL删除成功
-2、新创建的同名CL正常可用，插入数据，数据可正常压缩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不开启压缩，在表中插入大量数据（如1G），修改为snappy压缩后再次插入大量记录（如1G）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入1条16M大小的记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>批量更新已压缩和未压缩的记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志满导致事务回滚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试字典是否有无限膨胀的情况</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点所在主机磁盘满</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点所在主机CPU满</t>
+    <t>aggregate查询</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增压缩算法，需要验证集合/数据操作lzw压缩功能</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群模式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持单机、集群模式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3组3节点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖不同集合类型：普通表、hash表、range表、垂直分区表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行SQL创建CL，并指定lzw压缩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建字典并压缩记录后删除CL，删除CL后再次创建同名CL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启压缩后，不支持修改关闭压缩；
+指定压缩算法后不支持修改压缩算法。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂不支持修改压缩方式和压缩算法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂不支持修改压缩类型和压缩算法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改失败，提示参数错误</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改为LSW压缩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入16M大小的记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录，记录间子串重复率高</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录，记录间子串重复率低</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建lzw压缩表，覆盖不同集合类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据压缩后执行事务操作，包括事务提交和回滚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计说明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能测试</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性测试</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、新增压缩算法对原有压缩方式（不开启压缩、开启Snappy压缩）不影响
+2、新增压缩算法需要保证数据库操作、数据操作功能正确性，且压缩比要有明显提升
+3、性能比原来要有所提升</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1299,12 +1563,20 @@
 so，主要考虑压缩、解压过程中节点/主机/资源消耗异常</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>数据已压缩，并发做增删改查操作时数据节点异常</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建字典过程中数据节点异常</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="26">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1440,23 +1712,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
@@ -1495,16 +1750,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <strike/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1739,37 +1987,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right/>
@@ -1818,6 +2035,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1840,7 +2094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1854,12 +2108,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1908,7 +2156,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1917,24 +2165,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1950,24 +2190,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1977,39 +2229,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2019,28 +2238,70 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Calculation" xfId="4" builtinId="22"/>
@@ -2345,62 +2606,60 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="28.75" customWidth="1"/>
+    <col min="2" max="4" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="35"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="36"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="37"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="38"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="58.5" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
+      <c r="A7" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="71"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -2417,7 +2676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.875" customWidth="1"/>
@@ -2427,83 +2686,87 @@
     <col min="5" max="5" width="28.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+    <row r="1" spans="1:5" ht="24.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="D2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="5" customFormat="1" ht="45" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="7" customFormat="1" ht="45" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="10"/>
+      <c r="D3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" ht="40.5">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5"/>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>171</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>172</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="38"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2512,864 +2775,743 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" s="7" customFormat="1" ht="45" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="10"/>
+    <row r="9" spans="1:5" s="5" customFormat="1" ht="45" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="42" customHeight="1">
-      <c r="A10" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="1"/>
+      <c r="A10" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="27">
-      <c r="A11" s="38"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="27">
       <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>173</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="32" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="38"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="65" t="s">
-        <v>176</v>
+      <c r="C15" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="36" t="s">
-        <v>12</v>
+      <c r="A16" s="32" t="s">
+        <v>11</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="38"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="36" t="s">
-        <v>150</v>
+      <c r="A18" s="32" t="s">
+        <v>129</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="38"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="36" t="s">
-        <v>28</v>
+      <c r="A20" s="32" t="s">
+        <v>160</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="37"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="38"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>118</v>
+      <c r="C22" s="26" t="s">
+        <v>161</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="38"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" s="7" customFormat="1" ht="45" customHeight="1">
-      <c r="A26" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+    <row r="26" spans="1:5">
+      <c r="A26" s="34"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" s="5" customFormat="1" ht="45" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="1" t="s">
-        <v>26</v>
+      <c r="A28" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>23</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A29" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" s="18"/>
+    <row r="29" spans="1:5">
+      <c r="A29" s="56"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A30" s="37"/>
-      <c r="B30" s="37"/>
+      <c r="A30" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>177</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="18"/>
+        <v>158</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="16"/>
     </row>
     <row r="31" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A31" s="37"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="37"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="33"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" ht="39" customHeight="1">
-      <c r="A33" s="37"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="E33" s="18"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="33"/>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" customHeight="1">
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="33"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="1:5" ht="27" customHeight="1">
-      <c r="A34" s="37"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" s="18"/>
+        <v>106</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="16"/>
     </row>
     <row r="35" spans="1:5" ht="27" customHeight="1">
-      <c r="A35" s="37"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="18"/>
+        <v>115</v>
+      </c>
+      <c r="D35" s="33"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="18"/>
+        <v>116</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A37" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>30</v>
+      <c r="A37" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>169</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
     <row r="38" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="33"/>
       <c r="C38" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
     <row r="39" spans="1:5" ht="40.5" customHeight="1">
-      <c r="A39" s="38"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="1" t="s">
-        <v>179</v>
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="26" t="s">
+        <v>152</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" ht="27">
-      <c r="A40" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>49</v>
+    <row r="40" spans="1:5" ht="40.5">
+      <c r="A40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>151</v>
       </c>
       <c r="E40" s="1"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="36" t="s">
-        <v>109</v>
+      <c r="B41" s="32" t="s">
+        <v>93</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="37"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="37"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="1" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="37"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="33"/>
       <c r="C44" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="37"/>
-      <c r="B45" s="37"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="33"/>
       <c r="C45" s="1" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="37"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="33"/>
       <c r="C46" s="1" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="37"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="30" t="s">
-        <v>149</v>
+      <c r="A47" s="33"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="37"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
     <row r="49" spans="1:7" ht="40.5">
-      <c r="A49" s="37"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="24" t="s">
-        <v>158</v>
+      <c r="A49" s="33"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>111</v>
+        <v>137</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A50" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="B50" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>161</v>
+      <c r="A50" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>139</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="G50" s="16"/>
+      <c r="G50" s="14"/>
     </row>
     <row r="51" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A51" s="37"/>
-      <c r="B51" s="37"/>
-      <c r="C51" s="23" t="s">
-        <v>181</v>
+      <c r="A51" s="33"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="G51" s="16"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A52" s="37"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="G52" s="16"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A53" s="37"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A54" s="38"/>
-      <c r="B54" s="38"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A55" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>59</v>
+      <c r="A55" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>47</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A56" s="37"/>
-      <c r="B56" s="37"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="33"/>
       <c r="C56" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:7" ht="67.5" customHeight="1">
-      <c r="A57" s="38"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="19" t="s">
-        <v>61</v>
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E57" s="1"/>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1">
-      <c r="A58" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" s="36" t="s">
-        <v>164</v>
+      <c r="A58" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>141</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1">
-      <c r="A59" s="37"/>
-      <c r="B59" s="37"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="33"/>
       <c r="C59" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:7" ht="24" customHeight="1">
-      <c r="A60" s="38"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="28" t="s">
-        <v>165</v>
+      <c r="A60" s="34"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="26" t="s">
+        <v>142</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
     <row r="61" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A61" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="36"/>
+      <c r="A61" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="32"/>
       <c r="C61" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A62" s="37"/>
-      <c r="B62" s="37"/>
+      <c r="A62" s="33"/>
+      <c r="B62" s="33"/>
       <c r="C62" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A63" s="38"/>
-      <c r="B63" s="38"/>
+      <c r="A63" s="34"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="36" t="s">
-        <v>53</v>
+      <c r="B64" s="32" t="s">
+        <v>41</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="36" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>43</v>
       </c>
       <c r="E64" s="1"/>
     </row>
     <row r="65" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A65" s="37"/>
-      <c r="B65" s="37"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
       <c r="C65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="33"/>
+      <c r="E65" s="1"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A66" s="33"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D65" s="37"/>
-      <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A66" s="37"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" s="38"/>
+      <c r="D66" s="34"/>
       <c r="E66" s="1"/>
     </row>
     <row r="67" spans="1:5" ht="100.5" customHeight="1">
-      <c r="A67" s="37"/>
-      <c r="B67" s="37"/>
-      <c r="C67" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E67" s="17"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="15"/>
     </row>
     <row r="68" spans="1:5" ht="98.25" customHeight="1">
-      <c r="A68" s="37"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>128</v>
+      <c r="A68" s="33"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="E68" s="1"/>
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="38"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="29" t="s">
-        <v>54</v>
+      <c r="A69" s="34"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E69" s="1"/>
     </row>
     <row r="70" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A70" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="36" t="s">
-        <v>43</v>
+      <c r="A70" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
     <row r="71" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A71" s="37"/>
-      <c r="B71" s="37"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="33"/>
       <c r="C71" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="38"/>
-      <c r="B72" s="38"/>
+      <c r="A72" s="34"/>
+      <c r="B72" s="34"/>
       <c r="C72" s="1" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
     <row r="73" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A73" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="36"/>
-      <c r="C73" s="1" t="s">
-        <v>129</v>
+      <c r="A73" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="32"/>
+      <c r="C73" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="38"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="28" t="s">
-        <v>169</v>
+      <c r="A74" s="34"/>
+      <c r="B74" s="34"/>
+      <c r="C74" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
     </row>
-    <row r="75" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A75" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="47"/>
-    </row>
-    <row r="76" spans="1:5" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A76" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="B76" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-    </row>
-    <row r="77" spans="1:5" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A77" s="43"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-    </row>
-    <row r="78" spans="1:5" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A78" s="43"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-    </row>
-    <row r="79" spans="1:5" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A79" s="43"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-    </row>
-    <row r="80" spans="1:5" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A80" s="44"/>
-      <c r="B80" s="44"/>
-      <c r="C80" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-    </row>
-    <row r="81" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A81" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B81" s="46"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="47"/>
-    </row>
-    <row r="82" spans="1:5" ht="99" customHeight="1">
-      <c r="A82" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="B82" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-    </row>
-    <row r="83" spans="1:5" s="15" customFormat="1">
-      <c r="A83" s="43"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-    </row>
-    <row r="84" spans="1:5" s="15" customFormat="1">
-      <c r="A84" s="44"/>
-      <c r="B84" s="44"/>
-      <c r="C84" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-    </row>
-    <row r="85" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A85" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="B85" s="49"/>
-      <c r="C85" s="49"/>
-      <c r="D85" s="49"/>
-      <c r="E85" s="50"/>
-    </row>
-    <row r="86" spans="1:5" s="15" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A86" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D86" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="E86" s="67"/>
-    </row>
-    <row r="87" spans="1:5" s="15" customFormat="1" ht="27">
-      <c r="A87" s="66"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D87" s="44"/>
-      <c r="E87" s="68"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="66"/>
-      <c r="B88" s="66"/>
-      <c r="C88" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E88" s="14"/>
-    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="35">
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A41:A49"/>
+    <mergeCell ref="B41:B49"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B30:B36"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A64:A69"/>
     <mergeCell ref="B64:B69"/>
@@ -3381,39 +3523,11 @@
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="A61:A63"/>
     <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="A50:A54"/>
     <mergeCell ref="B50:B54"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="B41:B49"/>
-    <mergeCell ref="A29:A36"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="A76:A80"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="D30:D33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3424,285 +3538,461 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.5" customWidth="1"/>
-    <col min="2" max="2" width="29.125" customWidth="1"/>
-    <col min="3" max="4" width="25.5" customWidth="1"/>
-    <col min="5" max="5" width="29.25" customWidth="1"/>
-    <col min="6" max="6" width="26.25" customWidth="1"/>
-    <col min="7" max="7" width="28.875" customWidth="1"/>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="29.25" customWidth="1"/>
+    <col min="5" max="5" width="26.25" customWidth="1"/>
+    <col min="6" max="6" width="28.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="34.5" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A1" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
+    </row>
+    <row r="2" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27">
+      <c r="A3" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="65"/>
+      <c r="B4" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="52"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="66"/>
+      <c r="B5" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="52"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="66"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="66"/>
+      <c r="B7" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="52"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="66"/>
+      <c r="B8" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="52"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="66"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="52"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="66"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="40.5">
-      <c r="A2" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="53"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="63"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="53"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="20" t="s">
+      <c r="E10" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="52"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="66"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="63"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="53"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="63"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="53"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="20" t="s">
+      <c r="E11" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="52"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="66"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="63"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="63"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="63"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="63"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="63"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="63"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="53"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="63"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="53"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="63"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="53"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="69" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="63"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="53"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="69" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="63"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="53"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="63"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="53"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="63"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="54"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="69" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="64"/>
+      <c r="E12" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="52"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="66"/>
+      <c r="B13" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="52"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="66"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="52"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="66"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="52"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="66"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="52"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="66"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="52"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="66"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="52"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="66"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G2:G18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A19"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F3:F19"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="30.875" customWidth="1"/>
+    <col min="3" max="4" width="36.125" customWidth="1"/>
+    <col min="5" max="5" width="32.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A1" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A2" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+    </row>
+    <row r="3" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A3" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A8" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="47"/>
+    </row>
+    <row r="9" spans="1:5" ht="99" customHeight="1">
+      <c r="A9" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" s="13" customFormat="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" spans="1:5" s="13" customFormat="1">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A12" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
+    </row>
+    <row r="13" spans="1:5" s="13" customFormat="1" ht="40.5" customHeight="1">
+      <c r="A13" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="42"/>
+    </row>
+    <row r="14" spans="1:5" s="13" customFormat="1" ht="27">
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="43"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A9:A11"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/数据压缩/compress测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/数据压缩/compress测试设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="1" r:id="rId1"/>
@@ -150,6 +150,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="C30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+其他测试点必备步骤，不需要单独写测试点</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C39" authorId="0">
       <text>
         <r>
@@ -856,18 +882,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>创建单键非唯一索引，批量插入记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建复合键唯一索引，批量修改记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建强制唯一索引，批量查询记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>功能正常可用，数据有压缩，压缩比40%以上</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -944,10 +958,6 @@
   </si>
   <si>
     <t>执行truncate并再次插入数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行remove()删除所有数据并再次插入数据</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1569,6 +1579,22 @@
   </si>
   <si>
     <t>构建字典过程中数据节点异常</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行remove()删除所有数据并再次插入数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建单键非唯一索引，批量插入记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建复合键唯一索引，批量修改记录</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建强制唯一索引，批量查询记录</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2175,6 +2201,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2190,9 +2238,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2219,88 +2327,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2616,50 +2642,50 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="31"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="37" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="32"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="33"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="34"/>
+      <c r="A5" s="42"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="58.5" customHeight="1">
-      <c r="A7" s="69" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="71"/>
+      <c r="A7" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="45"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -2687,17 +2713,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.75" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+      <c r="A1" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>19</v>
@@ -2723,45 +2749,45 @@
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" ht="40.5">
       <c r="A4" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>171</v>
+      <c r="B5" s="48" t="s">
+        <v>167</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>172</v>
+        <v>52</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>168</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="34"/>
-      <c r="B6" s="59"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
@@ -2775,7 +2801,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2784,7 +2810,7 @@
     </row>
     <row r="9" spans="1:5" s="5" customFormat="1" ht="45" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>22</v>
@@ -2793,33 +2819,33 @@
         <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="42" customHeight="1">
-      <c r="A10" s="32" t="s">
-        <v>126</v>
+      <c r="A10" s="40" t="s">
+        <v>122</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="27">
-      <c r="A11" s="34"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -2828,13 +2854,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -2844,88 +2870,88 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="34"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="1"/>
       <c r="C15" s="26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="34"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="32" t="s">
-        <v>129</v>
+      <c r="A18" s="40" t="s">
+        <v>125</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="34"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="32" t="s">
-        <v>160</v>
+      <c r="A20" s="40" t="s">
+        <v>156</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="33"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -2934,10 +2960,10 @@
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="34"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="1"/>
       <c r="C22" s="26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2948,152 +2974,152 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="33"/>
+      <c r="A25" s="41"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="34"/>
+      <c r="A26" s="42"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
     <row r="27" spans="1:5" s="5" customFormat="1" ht="45" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="57" t="s">
+      <c r="A28" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="31" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="56"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="57" t="s">
-        <v>165</v>
+      <c r="A29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="31" t="s">
+        <v>161</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>177</v>
+      <c r="A30" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>173</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>123</v>
+        <v>154</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>119</v>
       </c>
       <c r="E30" s="16"/>
     </row>
     <row r="31" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="33"/>
+        <v>127</v>
+      </c>
+      <c r="D31" s="41"/>
       <c r="E31" s="16"/>
     </row>
     <row r="32" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="33"/>
+        <v>128</v>
+      </c>
+      <c r="D32" s="41"/>
       <c r="E32" s="16"/>
     </row>
     <row r="33" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" s="33"/>
+        <v>129</v>
+      </c>
+      <c r="D33" s="41"/>
       <c r="E33" s="16"/>
     </row>
     <row r="34" spans="1:5" ht="27" customHeight="1">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>103</v>
       </c>
       <c r="E34" s="16"/>
     </row>
     <row r="35" spans="1:5" ht="27" customHeight="1">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="33"/>
+        <v>111</v>
+      </c>
+      <c r="D35" s="41"/>
       <c r="E35" s="16"/>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="34"/>
+        <v>112</v>
+      </c>
+      <c r="D36" s="42"/>
       <c r="E36" s="16"/>
     </row>
     <row r="37" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="32" t="s">
-        <v>169</v>
+      <c r="B37" s="40" t="s">
+        <v>165</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
@@ -3102,22 +3128,22 @@
       <c r="E37" s="1"/>
     </row>
     <row r="38" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
     <row r="39" spans="1:5" ht="40.5" customHeight="1">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="26" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -3127,29 +3153,29 @@
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E40" s="1"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="32" t="s">
-        <v>93</v>
+      <c r="B41" s="40" t="s">
+        <v>89</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="1" t="s">
         <v>25</v>
       </c>
@@ -3157,120 +3183,120 @@
       <c r="E42" s="1"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="41"/>
       <c r="C44" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="41"/>
       <c r="C45" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="33"/>
-      <c r="B46" s="33"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="41"/>
       <c r="C46" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="33"/>
-      <c r="B47" s="33"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="41"/>
       <c r="C47" s="26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="33"/>
-      <c r="B48" s="33"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
       <c r="C48" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
     <row r="49" spans="1:7" ht="40.5">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A50" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>140</v>
-      </c>
       <c r="C50" s="21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="G50" s="14"/>
     </row>
     <row r="51" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="41"/>
       <c r="C51" s="21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="41"/>
       <c r="C52" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A53" s="33"/>
-      <c r="B53" s="33"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="41"/>
       <c r="C53" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="42"/>
       <c r="C54" s="1" t="s">
         <v>26</v>
       </c>
@@ -3278,58 +3304,58 @@
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A55" s="32" t="s">
+      <c r="A55" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="41"/>
       <c r="C56" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:7" ht="67.5" customHeight="1">
-      <c r="A57" s="34"/>
-      <c r="B57" s="34"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="42"/>
       <c r="C57" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E57" s="1"/>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1">
-      <c r="A58" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>141</v>
+      <c r="A58" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="40" t="s">
+        <v>137</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1">
-      <c r="A59" s="33"/>
-      <c r="B59" s="33"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="41"/>
       <c r="C59" s="1" t="s">
         <v>28</v>
       </c>
@@ -3337,162 +3363,181 @@
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:7" ht="24" customHeight="1">
-      <c r="A60" s="34"/>
-      <c r="B60" s="34"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="42"/>
       <c r="C60" s="26" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
     <row r="61" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A61" s="32" t="s">
+      <c r="A61" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B61" s="32"/>
+      <c r="B61" s="40"/>
       <c r="C61" s="1" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A62" s="33"/>
-      <c r="B62" s="33"/>
+      <c r="A62" s="41"/>
+      <c r="B62" s="41"/>
       <c r="C62" s="1" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A63" s="34"/>
-      <c r="B63" s="34"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
       <c r="C63" s="1" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="32" t="s">
+      <c r="B64" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E64" s="1"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A65" s="41"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="41"/>
+      <c r="E65" s="1"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A66" s="41"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="42"/>
+      <c r="E66" s="1"/>
+    </row>
+    <row r="67" spans="1:5" ht="100.5" customHeight="1">
+      <c r="A67" s="41"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E67" s="15"/>
+    </row>
+    <row r="68" spans="1:5" ht="98.25" customHeight="1">
+      <c r="A68" s="41"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" s="1"/>
+    </row>
+    <row r="69" spans="1:5" ht="18" customHeight="1">
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A65" s="33"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="33"/>
-      <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A66" s="33"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D66" s="34"/>
-      <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" ht="100.5" customHeight="1">
-      <c r="A67" s="33"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="E67" s="15"/>
-    </row>
-    <row r="68" spans="1:5" ht="98.25" customHeight="1">
-      <c r="A68" s="33"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="E69" s="1"/>
     </row>
     <row r="70" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="32" t="s">
-        <v>178</v>
+      <c r="B70" s="40" t="s">
+        <v>174</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
     <row r="71" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A71" s="33"/>
-      <c r="B71" s="33"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="41"/>
       <c r="C71" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="34"/>
-      <c r="B72" s="34"/>
+      <c r="A72" s="42"/>
+      <c r="B72" s="42"/>
       <c r="C72" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
     <row r="73" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A73" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="32"/>
+      <c r="A73" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" s="40"/>
       <c r="C73" s="26" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="34"/>
-      <c r="B74" s="34"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="42"/>
       <c r="C74" s="26" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="D30:D33"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D64:D66"/>
     <mergeCell ref="A73:A74"/>
@@ -3509,25 +3554,6 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="D30:D33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3549,253 +3575,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
+      <c r="A1" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:6" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
       <c r="F2" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27">
+      <c r="A3" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="58" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="27">
-      <c r="A3" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>124</v>
-      </c>
-    </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="65"/>
-      <c r="B4" s="64" t="s">
-        <v>67</v>
+      <c r="A4" s="53"/>
+      <c r="B4" s="36" t="s">
+        <v>63</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="52"/>
+        <v>63</v>
+      </c>
+      <c r="F4" s="59"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="66"/>
-      <c r="B5" s="64" t="s">
-        <v>68</v>
+      <c r="A5" s="54"/>
+      <c r="B5" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="52"/>
+        <v>64</v>
+      </c>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="66"/>
-      <c r="B6" s="64"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="18"/>
       <c r="D6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="59"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="54"/>
+      <c r="B7" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="59"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="54"/>
+      <c r="B8" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="59"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="54"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="59"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="54"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="59"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="54"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="59"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="54"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="52"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="66"/>
-      <c r="B7" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="52"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="66"/>
-      <c r="B8" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="52"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="66"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="52"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="66"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="52"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="66"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="52"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="66"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>84</v>
-      </c>
       <c r="E12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="52"/>
+        <v>71</v>
+      </c>
+      <c r="F12" s="59"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="66"/>
-      <c r="B13" s="64" t="s">
-        <v>63</v>
+      <c r="A13" s="54"/>
+      <c r="B13" s="36" t="s">
+        <v>59</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="52"/>
+        <v>59</v>
+      </c>
+      <c r="F13" s="59"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="66"/>
-      <c r="B14" s="64"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
-      <c r="F14" s="52"/>
+      <c r="F14" s="59"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="66"/>
-      <c r="B15" s="64"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="29" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
-      <c r="F15" s="52"/>
+      <c r="F15" s="59"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="66"/>
-      <c r="B16" s="64"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="29" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
-      <c r="F16" s="52"/>
+      <c r="F16" s="59"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="66"/>
-      <c r="B17" s="64"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
-      <c r="F17" s="52"/>
+      <c r="F17" s="59"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="66"/>
-      <c r="B18" s="64"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="52"/>
+      <c r="F18" s="59"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="66"/>
-      <c r="B19" s="64"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="29" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
-      <c r="F19" s="53"/>
+      <c r="F19" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3822,161 +3848,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>180</v>
+      <c r="A1" s="33" t="s">
+        <v>176</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C1" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A2" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
+      <c r="A2" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
     </row>
     <row r="3" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>147</v>
+      <c r="A3" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="54" t="s">
-        <v>148</v>
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" s="13" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="68"/>
       <c r="C7" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A8" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="47"/>
+      <c r="A8" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:5" ht="99" customHeight="1">
-      <c r="A9" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>149</v>
+      <c r="A9" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>145</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" s="13" customFormat="1">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" s="13" customFormat="1">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A12" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
+      <c r="A12" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
     </row>
     <row r="13" spans="1:5" s="13" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>58</v>
+      <c r="A13" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="69" t="s">
+        <v>54</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="42"/>
+        <v>108</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5" s="13" customFormat="1" ht="27">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="43"/>
+        <v>109</v>
+      </c>
+      <c r="D14" s="68"/>
+      <c r="E14" s="71"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E15" s="12"/>
     </row>
